--- a/tame_output/ON/bt/strategyON_20240318.xlsx
+++ b/tame_output/ON/bt/strategyON_20240318.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-331.7%</t>
+          <t>-331.4%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-129.2%</t>
+          <t>-129.1%</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-65.6%</t>
+          <t>-65.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-35.7%</t>
         </is>
       </c>
     </row>
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-1.701186274302761</v>
+        <v>-1.698166451458426</v>
       </c>
       <c r="E1906" t="n">
-        <v>2.470317070927144</v>
+        <v>2.471525000064879</v>
       </c>
       <c r="F1906" t="n">
-        <v>1.584220221532464</v>
+        <v>1.5872400443768</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.101680137881475</v>
+        <v>4.103492031588076</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240318.xlsx
+++ b/tame_output/ON/bt/strategyON_20240318.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-59.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,27 +1007,27 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-53.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>490.3%</t>
+          <t>489.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-331.4%</t>
+          <t>-348.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-129.1%</t>
+          <t>-135.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,27 +1323,27 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-65.3%</t>
+          <t>-82.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-45.7%</t>
         </is>
       </c>
     </row>
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-1.698166451458426</v>
+        <v>-1.865822236662166</v>
       </c>
       <c r="E1906" t="n">
-        <v>2.471525000064879</v>
+        <v>2.404462685983382</v>
       </c>
       <c r="F1906" t="n">
-        <v>1.5872400443768</v>
+        <v>1.41958425917306</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.103492031588076</v>
+        <v>4.002898560465832</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240318.xlsx
+++ b/tame_output/ON/bt/strategyON_20240318.xlsx
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>

--- a/tame_output/ON/bt/strategyON_20240318.xlsx
+++ b/tame_output/ON/bt/strategyON_20240318.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>-13.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-59.5%</t>
+          <t>-61.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,11 +969,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-36.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-55.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>643.0%</t>
+          <t>640.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-339.2%</t>
+          <t>-364.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1127,11 +1127,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-130.9%</t>
+          <t>-158.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,32 +1323,32 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-39.2%</t>
+          <t>317.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-68.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-95.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-70.2%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-7.214236874966595</v>
+        <v>-7.482127681208075</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.2730092725216475</v>
+        <v>0.1658529500250556</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.115563744450082</v>
+        <v>-1.353135803149832</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.489722200151984</v>
+        <v>2.347178964932134</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-7.151167642660255</v>
+        <v>-7.419058448901735</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.3009306940732981</v>
+        <v>0.1937743715767062</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.144077307132317</v>
+        <v>-1.381649365832067</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.475307791171758</v>
+        <v>2.332764555951908</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-7.099152128691443</v>
+        <v>-7.367042934932923</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.325727235347224</v>
+        <v>0.2185709128506321</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.144077307132317</v>
+        <v>-1.381649365832067</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.479298126858159</v>
+        <v>2.336754891638309</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-6.923582459770539</v>
+        <v>-7.191473266012019</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.394479876016844</v>
+        <v>0.2873235535202516</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.144077307132317</v>
+        <v>-1.381649365832067</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.477822899959417</v>
+        <v>2.335279664739567</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-6.72631305404254</v>
+        <v>-6.994203860284021</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.4884410484729154</v>
+        <v>0.3812847259763235</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.9468079014043186</v>
+        <v>-1.184379960104069</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.611237953561088</v>
+        <v>2.468694718341238</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-6.527160946805441</v>
+        <v>-6.795051753046922</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.5550507577210722</v>
+        <v>0.4478944352244798</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.7814853754545052</v>
+        <v>-1.019057434154255</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.697380335484293</v>
+        <v>2.554837100264443</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-6.30131579408603</v>
+        <v>-6.569206600327511</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.654967891845045</v>
+        <v>0.5478115693484531</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.7395586998673416</v>
+        <v>-0.9771307585670916</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.7321154138728</v>
+        <v>2.58957217865295</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-6.015040981763336</v>
+        <v>-6.282931788004817</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.7706169613301816</v>
+        <v>0.6634606388335897</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.7395586998673416</v>
+        <v>-0.9771307585670916</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.733254558428859</v>
+        <v>2.590711323209009</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-5.788245154690003</v>
+        <v>-6.056135960931483</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.8639690663216228</v>
+        <v>0.7568127438250305</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.6714447552457971</v>
+        <v>-0.9090168139455471</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.776756699363893</v>
+        <v>2.634213464144043</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-5.504336423761254</v>
+        <v>-5.772227230002734</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.983266262931759</v>
+        <v>0.8761099404351667</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.6714447552457971</v>
+        <v>-0.9090168139455471</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.78249040360253</v>
+        <v>2.63994716838268</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-5.257349173568302</v>
+        <v>-5.525239979809782</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.072323900615074</v>
+        <v>0.9651675781184825</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.424457505052845</v>
+        <v>-0.662029563752595</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.920945491324436</v>
+        <v>2.778402256104586</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-4.993512306364233</v>
+        <v>-5.261403112605713</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.167975166183794</v>
+        <v>1.060818843687203</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.424457505052845</v>
+        <v>-0.662029563752595</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.911062010011528</v>
+        <v>2.768518774791678</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-4.726270505495836</v>
+        <v>-4.994161311737316</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.27303732603178</v>
+        <v>1.165881003535187</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.424457505052845</v>
+        <v>-0.662029563752595</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.909227449512155</v>
+        <v>2.766684214292304</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-4.450461342095352</v>
+        <v>-4.718352148336832</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.383060676418512</v>
+        <v>1.27590435392192</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.3354381967741115</v>
+        <v>-0.5730102554738615</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.962338719505934</v>
+        <v>2.819795484286084</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-4.181393754328372</v>
+        <v>-4.449284560569852</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.491356217670798</v>
+        <v>1.384199895174206</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.0663706090071321</v>
+        <v>-0.3039426677068822</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.124447778311615</v>
+        <v>2.981904543091765</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-3.917333816005576</v>
+        <v>-4.185224622247056</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.583719876838164</v>
+        <v>1.476563554341572</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.1976893293156641</v>
+        <v>-0.03988272938408599</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.269623425143541</v>
+        <v>3.12708018992369</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-3.210254192500738</v>
+        <v>-3.478144998742219</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.863764692579798</v>
+        <v>1.756608370083206</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.1976893293156641</v>
+        <v>-0.03988272938408599</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.26683639148324</v>
+        <v>3.12429315626339</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-2.960613162514787</v>
+        <v>-3.228503968756267</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.96396472846202</v>
+        <v>1.856808405965428</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.4473303593016158</v>
+        <v>0.2097583006018657</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.416964633362652</v>
+        <v>3.274421398142802</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-2.706071263173711</v>
+        <v>-2.973962069415192</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.065148309419207</v>
+        <v>1.957991986922615</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.7018722586426913</v>
+        <v>0.4643001999429412</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.569056594188054</v>
+        <v>3.426513358968204</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-2.472590040944113</v>
+        <v>-2.740480847185593</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.166465227148899</v>
+        <v>2.059308904652307</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.9353534808722899</v>
+        <v>0.6977814221725398</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.717069756363666</v>
+        <v>3.574526521143816</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-2.29288151080024</v>
+        <v>-2.56077231704172</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.235456428893489</v>
+        <v>2.128300106396897</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.992524985034986</v>
+        <v>0.7549529263352359</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.748480448548325</v>
+        <v>3.605937213328474</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-2.160606037169353</v>
+        <v>-2.428496843410834</v>
       </c>
       <c r="E1905" t="n">
-        <v>2.283734105092871</v>
+        <v>2.176577782596279</v>
       </c>
       <c r="F1905" t="n">
-        <v>1.124800458665873</v>
+        <v>0.8872283999661226</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.823213219473883</v>
+        <v>3.680669984254033</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-1.970006362496201</v>
+        <v>-2.237897168737681</v>
       </c>
       <c r="E1906" t="n">
-        <v>2.362789035649769</v>
+        <v>2.255632713153177</v>
       </c>
       <c r="F1906" t="n">
-        <v>1.315400133339026</v>
+        <v>1.077828074639275</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.940388084965412</v>
+        <v>3.797844849745561</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.531260009586252</v>
+        <v>3.415092192862867</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>2.984116385736119</v>
       </c>
       <c r="D1907" t="n">
-        <v>-1.776213505433914</v>
+        <v>-2.02538623687585</v>
       </c>
       <c r="E1907" t="n">
-        <v>2.453212519698342</v>
+        <v>2.173605466672031</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.509192990401312</v>
+        <v>1.290339006501106</v>
       </c>
       <c r="G1907" t="n">
-        <v>4.069570140426443</v>
+        <v>3.758319789636783</v>
       </c>
     </row>
   </sheetData>
